--- a/AtchisonRegime/Outputs/Japan/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Japan/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
@@ -1396,13 +1396,13 @@
         <v>45565</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1162222403462649</v>
+        <v>0.136670511310087</v>
       </c>
     </row>
   </sheetData>
